--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 млрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ/дв 16,07,26 млрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA605C4-088C-4C39-ADE2-9D53EEF14AE6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF51691-795B-4108-9C83-75EF91403DB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="169">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -536,6 +536,9 @@
   <si>
     <t>Чебуреки сочные, ВЕС, куриные жарен. зам  ПОКОМ</t>
   </si>
+  <si>
+    <t>нет</t>
+  </si>
 </sst>
 </file>
 
@@ -1290,7 +1293,9 @@
       <c r="AD4" s="17"/>
       <c r="AE4" s="17"/>
       <c r="AF4" s="6"/>
-      <c r="AG4" s="8"/>
+      <c r="AG4" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="AH4" s="17"/>
       <c r="AI4" s="17"/>
       <c r="AJ4" s="17"/>
@@ -3358,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" ref="Q11:Q49" si="11">$Q$1*P22-O22-F22</f>
+        <f t="shared" ref="Q22:Q46" si="11">$Q$1*P22-O22-F22</f>
         <v>65</v>
       </c>
       <c r="R22" s="4">
@@ -5343,7 +5348,7 @@
         <v>75</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L68" si="12">E38-K38</f>
         <v>0</v>
       </c>
       <c r="M38" s="17"/>
@@ -5361,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="17">
-        <f t="shared" ref="S38:S69" si="14">(F38+O38+R38)/P38</f>
+        <f t="shared" ref="S38:S68" si="14">(F38+O38+R38)/P38</f>
         <v>41.6</v>
       </c>
       <c r="T38" s="17">
